--- a/artfynd/A 62142-2025 artfynd.xlsx
+++ b/artfynd/A 62142-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104657606</v>
+        <v>104657605</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516136.5205161104</v>
+        <v>516146</v>
       </c>
       <c r="R2" t="n">
-        <v>7288174.197819411</v>
+        <v>7288159</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,42 +785,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104657273</v>
+        <v>104657606</v>
       </c>
       <c r="B3" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221343</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516156.0095678459</v>
+        <v>516136</v>
       </c>
       <c r="R3" t="n">
-        <v>7288154.128645544</v>
+        <v>7288174</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,24 +862,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>157 m sträcka längs dike</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +884,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist, Engla Grönvall</t>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -930,42 +895,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104657605</v>
+        <v>104657273</v>
       </c>
       <c r="B4" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>221343</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -979,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516145.6754312912</v>
+        <v>516156</v>
       </c>
       <c r="R4" t="n">
-        <v>7288159.012414258</v>
+        <v>7288154</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,19 +972,14 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>157 m sträcka längs dike</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,7 +999,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+          <t>Väg och Miljö AB, Björn Almkvist, Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
